--- a/public/templates/office/Phase4_오픈소스_라이선스_검증서.xlsx
+++ b/public/templates/office/Phase4_오픈소스_라이선스_검증서.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSS_라이선스_검증" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_OSS_라이선스_검증내역" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,12 +30,13 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="001E293B"/>
-      <sz val="16"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="0064748B"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -44,11 +47,17 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00334155"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001E293B"/>
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -57,14 +66,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
+        <fgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,22 +116,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,296 +516,807 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OSS_라이선스_검증</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>[EMP-XLS-P4-03] 오픈소스 소프트웨어(OSS) 라이선스 검증서 및 SBOM 명세 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>엠파시 사업 및 개발 방법론 표준 시트 (주식회사 엠파시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="10" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
+          <t>SyncGuard AI 프론트엔드·백엔드·AI 추론 워커 사용 오픈소스 15종 라이선스 전수 점검 및 GPL 오염 0건 확인 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>오픈소스 라이브러리명</t>
+          <t>순번</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>컴포넌트 구분</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>오픈소스 패키지명</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>사용 버전</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>공식 라이선스</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>소스코드 공개 의무</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>상용 판매 가능 여부</t>
+          <t>라이선스 유형</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>의무 이행 사항</t>
+          <t>소스코드 공개의무</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>상용 독점 배포 가능</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>고지문(NOTICE) 반영</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>적합성 판정</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Spring Boot</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>3.4.0</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Backend API</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Spring Boot Starter Web / Security</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>3.3.4</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Backend API</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Spring Batch / Data JPA</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>5.1.2</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Backend API</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Project Lombok</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>1.18.34</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Backend API</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>PostgreSQL JDBC Driver (pgjdbc)</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>42.7.4</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>BSD-2-Clause</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Backend API</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Jackson Databind / Core</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>2.17.2</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>AI Worker</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>FastAPI</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>0.115.0</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>AI Worker</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Pydantic</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>2.9.2</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>AI Worker</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>LangChain Core / OpenAI SDK</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>0.3.1</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>AI Worker</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>pgvector-python / asyncpg</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>0.3.5</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>MIT / Apache-2.0</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>AI Worker</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>PyMuPDF (Archieve/Apache wrapper 제외 pypdf)</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>5.0.1</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>BSD-3-Clause</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>적격 (AGPL 배제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>React / React-DOM</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>18.3.1</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>5.6.2</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Ant Design / TailwindCSS</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>5.21.0</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>PostgreSQL &amp; pgvector Extension</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>16.4 / 0.7.4</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>PostgreSQL License</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Infra / Cache</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Redis (AWS ElastiCache Managed)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>BSD-3-Clause</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>적격</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>총 15개 핵심 패키지</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>GPL / AGPL 등 전염성 카피레프트 라이선스 0건 (100% Permissive 라이선스 준수)</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>MIT/Apache/BSD</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>공개 의무 없음</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>가능</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>저작권 고지문(NOTICE) 포함</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>적격</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Vue.js</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>3.5.0</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>공개 의무 없음</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>가능</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>저작권 고지문 포함</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>적격</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>PostgreSQL JDBC</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>42.7.2</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>BSD-2-Clause</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>공개 의무 없음</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>가능</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>저작권 고지문 포함</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>적격</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Lombok</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>1.18.36</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>공개 의무 없음</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>가능</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>컴파일 시점에만 사용</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>적격</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>AgentScope Java</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>0.1.0</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>공개 의무 없음</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>가능</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>저작권 고지문 포함</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>적격</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Jackson Core</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2.18.0</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>공개 의무 없음</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>가능</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>저작권 고지문 포함</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>적격</t>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>100% 가능</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>THIRD-PARTY-NOTICES.txt 수록</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>최종 적격</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/templates/office/Phase4_오픈소스_라이선스_검증서.xlsx
+++ b/public/templates/office/Phase4_오픈소스_라이선스_검증서.xlsx
@@ -533,14 +533,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[EMP-XLS-P4-03] 오픈소스 소프트웨어(OSS) 라이선스 검증서 및 SBOM 명세 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[EMP-XLS-P4-03] 오픈소스 소프트웨어(OSS) 라이선스 검증서 및 SBOM 명세 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SyncGuard AI 프론트엔드·백엔드·AI 추론 워커 사용 오픈소스 15종 라이선스 전수 점검 및 GPL 오염 0건 확인 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+          <t>SyncFlow AI 프론트엔드·백엔드·AI 추론 워커 사용 오픈소스 15종 라이선스 전수 점검 및 GPL 오염 0건 확인 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>오픈소스 패키지명</t>
+          <t>오픈소스 도면패키지명</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>총 15개 핵심 패키지</t>
+          <t>총 15개 핵심 도면패키지</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>GPL / AGPL 등 전염성 카피레프트 라이선스 0건 (100% Permissive 라이선스 준수)</t>
+          <t>GPL / AGPL 등 전염성 조항레프트 라이선스 0건 (100% Permissive 라이선스 준수)</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
